--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels-3x2/oocihm.22250/oocihm.22250.66.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels-3x2/oocihm.22250/oocihm.22250.66.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
